--- a/cleaning_pipeline_R/neotree_scripts/zim-scripts/Chinhoyi Provincial Hospital Admission - metadata.xlsx
+++ b/cleaning_pipeline_R/neotree_scripts/zim-scripts/Chinhoyi Provincial Hospital Admission - metadata.xlsx
@@ -1668,7 +1668,7 @@
         <v/>
       </c>
       <c r="O19" t="str">
-        <v>($NoPulseOx = false and $SatsAir &lt; 90) or ($NoPulseOx = false and $RR &gt; 60)</v>
+        <v>$SatsAir &lt; 90 or $RR &gt; 60</v>
       </c>
       <c r="P19" t="str">
         <v/>
@@ -2460,7 +2460,7 @@
         <v>BloodSugarmmol</v>
       </c>
       <c r="G31" t="str">
-        <v>Blood Sugar (mmol/L)      (2.5 - 4.5)</v>
+        <v>Blood Sugar (mmol/L)      (2.6 - 8.3)</v>
       </c>
       <c r="H31" t="str">
         <v>number</v>
@@ -2614,13 +2614,13 @@
         <v>No</v>
       </c>
       <c r="M33" t="str">
-        <v>$BloodSugarmmol &lt; 2.6 or $BloodSugarmg &lt; 46.8</v>
+        <v>$BloodSugarmmol &lt; 2.6 or $BloodSugarmg &lt; 47</v>
       </c>
       <c r="N33" t="str">
         <v>[{"value":"true","valueLabel":"Yes"},{"value":"false","valueLabel":"No"}]</v>
       </c>
       <c r="O33" t="str">
-        <v>$BloodSugarmmol &lt; 2.6 or $BloodSugarmg &lt; 46.8</v>
+        <v>$BloodSugarmmol &lt; 2.6 or $BloodSugarmg &lt; 47</v>
       </c>
       <c r="P33" t="str">
         <v/>
@@ -3093,7 +3093,7 @@
         <v/>
       </c>
       <c r="N40" t="str">
-        <v>[{"value":"AD","valueLabel":"Abdominal distension"},{"value":"BBA","valueLabel":"Born Before Arrival"},{"value":"Convulsions","valueLabel":"Convulsions"},{"value":"DIB","valueLabel":"Difficulty in breathing"},{"value":"DU","valueLabel":"Dumped baby"},{"value":"Fev","valueLabel":"Fever"},{"value":"FD","valueLabel":"Not sucking / feeding difficulties"},{"value":"GSchis","valueLabel":"Gastroschisis"},{"value":"NE","valueLabel":"Neonatal encephalopathy"},{"value":"HIVExp","valueLabel":"HIV Exposed"},{"value":"J","valueLabel":"Jaundice"},{"value":"LowBirthWeight","valueLabel":"Low Birth Weight"},{"value":"Apg","valueLabel":"Low Apgars"},{"value":"Mec","valueLabel":"Possible Meconium Aspiration"},{"value":"NTD","valueLabel":"Neural Tube Defect / Spina Bifida"},{"value":"Prem","valueLabel":"Prematurity"},{"value":"PremRDS","valueLabel":"Prematurity with RDS"},{"value":"SPn","valueLabel":"Severe Pneumonia"},{"value":"OM","valueLabel":"Omphalocele"},{"value":"Cong","valueLabel":"Other congenital abnormality"},{"value":"HBW","valueLabel":"Macrosomia (&gt;4000g)"},{"value":"Safe","valueLabel":"Safekeeping"},{"value":"Risk","valueLabel":"Risk factors for sepsis"},{"value":"NSep","valueLabel":"Suspected neonatal sepsis"},{"value":"O","valueLabel":"Other"}]</v>
+        <v>[{"value":"AD","valueLabel":"Abdominal distension"},{"value":"BBA","valueLabel":"Born Before Arrival"},{"value":"Convulsions","valueLabel":"Convulsions"},{"value":"DIB","valueLabel":"Difficulty in breathing"},{"value":"DU","valueLabel":"Dumped baby"},{"value":"Fev","valueLabel":"Fever"},{"value":"FD","valueLabel":"Not sucking / feeding difficulties"},{"value":"GSchis","valueLabel":"Gastroschisis"},{"value":"NE","valueLabel":"Neonatal encephalopathy"},{"value":"HIVExp","valueLabel":"HIV Exposed"},{"value":"J","valueLabel":"Jaundice"},{"value":"LowBirthWeight","valueLabel":"Low Birth Weight"},{"value":"Apg","valueLabel":"Low Apgars"},{"value":"Mec","valueLabel":"Possible Meconium Aspiration"},{"value":"NTD","valueLabel":"Neural Tube Defect / Spina Bifida"},{"value":"Prem","valueLabel":"Premature"},{"value":"PremRDS","valueLabel":"Prematurity with RDS"},{"value":"SPn","valueLabel":"Severe Pneumonia"},{"value":"OM","valueLabel":"Omphalocele"},{"value":"Cong","valueLabel":"Other congenital abnormality"},{"value":"HBW","valueLabel":"Macrosomia (&gt;4000g)"},{"value":"Safe","valueLabel":"Safekeeping"},{"value":"Risk","valueLabel":"Risk factors for sepsis"},{"value":"NSep","valueLabel":"Sepsis suspected"},{"value":"O","valueLabel":"Other"}]</v>
       </c>
       <c r="O40" t="str">
         <v/>
@@ -3161,7 +3161,7 @@
         <v/>
       </c>
       <c r="N41" t="str">
-        <v>[{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]},{"value":"Cong","valueLabel":"Other Congenital Abnormality","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AD","valueLabel":"Abdominal distension","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BBA","valueLabel":"Born Before Arrival","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Conv","valueLabel":"Convulsions","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DU","valueLabel":"Dumped baby","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Fev","valueLabel":"Fever","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DF","valueLabel":"Difficulty Feeding","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"GSchis","valueLabel":"Gastroschisis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HIE","valueLabel":"Hypoxic ischaemic encephalopathy","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HIVX","valueLabel":"HIV Exposed","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"J","valueLabel":"Jaundice","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"LBW","valueLabel":"Low birth weight","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Mec","valueLabel":"Possible Meconium aspiration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NTD","valueLabel":"Neural tube defect / spina bifida","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OM","valueLabel":"Omphalocele","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Prem","valueLabel":"Prematurity","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Pneum","valueLabel":"Pneumonia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"RDS","valueLabel":"Respiratory Distress","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OTH","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]},{"value":"Cong","valueLabel":"Other Congenital Abnormality","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AD","valueLabel":"Abdominal distension","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BBA","valueLabel":"Born Before Arrival","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Conv","valueLabel":"Convulsions","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DU","valueLabel":"Dumped baby","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Fev","valueLabel":"Fever","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DF","valueLabel":"Difficulty Feeding","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"GSchis","valueLabel":"Gastroschisis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HIE","valueLabel":"Hypoxic ischaemic encephalopathy","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HIVX","valueLabel":"HIV Exposed","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"J","valueLabel":"Jaundice","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"LBW","valueLabel":"Low birth weight","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Mec","valueLabel":"Possible Meconium aspiration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NTD","valueLabel":"Neural tube defect / spina bifida","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OM","valueLabel":"Omphalocele","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Prem","valueLabel":"Premature","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Pneum","valueLabel":"Pneumonia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"RDS","valueLabel":"Respiratory Distress","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OTH","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O41" t="str">
         <v/>
@@ -3430,7 +3430,7 @@
         <v>No</v>
       </c>
       <c r="M45" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N45" t="str">
         <v/>
@@ -3498,7 +3498,7 @@
         <v>No</v>
       </c>
       <c r="M46" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N46" t="str">
         <v/>
@@ -3566,7 +3566,7 @@
         <v>No</v>
       </c>
       <c r="M47" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N47" t="str">
         <v/>
@@ -4160,7 +4160,7 @@
         <v>Gestation</v>
       </c>
       <c r="G56" t="str">
-        <v>Gestational age at birth (weeks.days)</v>
+        <v>Estimated Gestational age at birth (weeks.days)</v>
       </c>
       <c r="H56" t="str">
         <v>number</v>
@@ -4184,7 +4184,7 @@
         <v/>
       </c>
       <c r="O56" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P56" t="str">
         <v/>
@@ -4252,7 +4252,7 @@
         <v>[{"value":"LMP","valueLabel":"Last Menstrual Period (LMP)"},{"value":"FH","valueLabel":"Fundal height"},{"value":"USS","valueLabel":"USS"}]</v>
       </c>
       <c r="O57" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P57" t="str">
         <v/>
@@ -4320,7 +4320,7 @@
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"U","valueLabel":"Unknown"}]</v>
       </c>
       <c r="O58" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P58" t="str">
         <v/>
@@ -4388,7 +4388,7 @@
         <v/>
       </c>
       <c r="O59" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P59" t="str">
         <v/>
@@ -4456,7 +4456,7 @@
         <v/>
       </c>
       <c r="O60" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P60" t="str">
         <v/>
@@ -4524,7 +4524,7 @@
         <v/>
       </c>
       <c r="O61" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P61" t="str">
         <v/>
@@ -7309,7 +7309,7 @@
         <v>$FeverSR = true</v>
       </c>
       <c r="N102" t="str">
-        <v>[{"value":"L24","valueLabel":"Less than 24hrs ago","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"1t2d","valueLabel":"1 - 2 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"2t3d","valueLabel":"2 -3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M3d","valueLabel":"more than 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"UNK","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"L24","valueLabel":"Less than 24hrs ago","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"1t2d","valueLabel":"1 - 2 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"2t3d","valueLabel":"2 -3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M3d","valueLabel":"more than 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Unk","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O102" t="str">
         <v>$FeverSR = true</v>
@@ -7445,7 +7445,7 @@
         <v>$RespSR != 'Norm'</v>
       </c>
       <c r="N104" t="str">
-        <v>[{"value":"L24","valueLabel":"Less than 24hrs ago","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"1t2d","valueLabel":"1 - 2 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"2t3d","valueLabel":"2 -3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M3d","valueLabel":"More than 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"UNK","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"L24","valueLabel":"Less than 24hrs ago","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"1t2d","valueLabel":"1 - 2 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"2t3d","valueLabel":"2 -3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M3d","valueLabel":"More than 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Unk","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O104" t="str">
         <v>$RespSR != 'Norm'</v>
@@ -7581,7 +7581,7 @@
         <v>$Vomiting != 'Norm'</v>
       </c>
       <c r="N106" t="str">
-        <v>[{"value":"L24","valueLabel":"Less than 24hrs ago","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"1t2d","valueLabel":"1 - 2 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"2t3d","valueLabel":"2 - 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M3d","valueLabel":"More than 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"UNK","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"L24","valueLabel":"Less than 24hrs ago","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"1t2d","valueLabel":"1 - 2 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"2t3d","valueLabel":"2 - 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M3d","valueLabel":"More than 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Unk","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O106" t="str">
         <v>$Vomiting != 'Norm'</v>
@@ -7921,7 +7921,7 @@
         <v>$Age &gt; 47.9 or $AgeEstimate = 'INF72' or $AgeEstimate = 'INF'</v>
       </c>
       <c r="N111" t="str">
-        <v>[{"value":"Norm","valueLabel":"Passing urine normally"},{"value":"NoPU","valueLabel":"Not passing urine"}]</v>
+        <v>[{"value":"Norm","valueLabel":"Passing urine normally"},{"value":"NPU","valueLabel":"Not passing urine"}]</v>
       </c>
       <c r="O111" t="str">
         <v/>
@@ -8057,7 +8057,7 @@
         <v>$SRNeuroOther != 'Norm'</v>
       </c>
       <c r="N113" t="str">
-        <v>[{"value":"L24","valueLabel":"Less than 24hrs ago","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"1t2d","valueLabel":"1 - 2 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"2t3d","valueLabel":"2 - 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M3","valueLabel":"More than 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"UNK","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"L24","valueLabel":"Less than 24hrs ago","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"1t2d","valueLabel":"1 - 2 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"2t3d","valueLabel":"2 - 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M3","valueLabel":"More than 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Unk","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O113" t="str">
         <v>$SRNeuroOther != 'Norm'</v>
@@ -8734,13 +8734,13 @@
         <v>No</v>
       </c>
       <c r="M123" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="N123" t="str">
         <v>[{"value":"true","valueLabel":"Yes"},{"value":"false","valueLabel":"No"}]</v>
       </c>
       <c r="O123" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P123" t="str">
         <v/>
@@ -8876,7 +8876,7 @@
         <v>[{"value":"HA","valueLabel":"Harare"},{"value":"BU","valueLabel":"Bulawayo"},{"value":"MC","valueLabel":"Mashonaland Central"},{"value":"ME","valueLabel":"Mashonaland East"},{"value":"MW","valueLabel":"Mashonaland West"},{"value":"MA","valueLabel":"Manicaland"},{"value":"MAS","valueLabel":"Masvingo"},{"value":"MN","valueLabel":"Matabeleland North"},{"value":"MS","valueLabel":"Matabeleland South"},{"value":"MID","valueLabel":"Midlands"}]</v>
       </c>
       <c r="O125" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P125" t="str">
         <v/>
@@ -8944,7 +8944,7 @@
         <v/>
       </c>
       <c r="O126" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P126" t="str">
         <v/>
@@ -9012,7 +9012,7 @@
         <v/>
       </c>
       <c r="O127" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P127" t="str">
         <v/>
@@ -9080,7 +9080,7 @@
         <v/>
       </c>
       <c r="O128" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P128" t="str">
         <v/>
@@ -9148,7 +9148,7 @@
         <v/>
       </c>
       <c r="O129" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P129" t="str">
         <v/>
@@ -9216,7 +9216,7 @@
         <v/>
       </c>
       <c r="O130" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P130" t="str">
         <v/>
@@ -9284,7 +9284,7 @@
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"}]</v>
       </c>
       <c r="O131" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P131" t="str">
         <v/>
@@ -9352,7 +9352,7 @@
         <v/>
       </c>
       <c r="O132" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P132" t="str">
         <v/>
@@ -9420,7 +9420,7 @@
         <v/>
       </c>
       <c r="O133" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P133" t="str">
         <v/>
@@ -9482,13 +9482,13 @@
         <v>No</v>
       </c>
       <c r="M134" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="N134" t="str">
         <v>[{"value":"MAR","valueLabel":"Married","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DIV","valueLabel":"Divorced","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"WID","valueLabel":"Widowed","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"S","valueLabel":"Single","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O134" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P134" t="str">
         <v/>
@@ -9553,10 +9553,10 @@
         <v/>
       </c>
       <c r="N135" t="str">
-        <v>[{"value":"A","valueLabel":"African"},{"value":"AA","valueLabel":"AfricanAmerican"},{"value":"AS","valueLabel":"Asian/Pacific Islander"},{"value":"W","valueLabel":"White"},{"value":"NA","valueLabel":"NativeAmerican"},{"value":"O","valueLabel":"Other"}]</v>
+        <v>[{"value":"A","valueLabel":"African"},{"value":"AS","valueLabel":"Asian/Pacific Islander"},{"value":"W","valueLabel":"White"},{"value":"NA","valueLabel":"NativeAmerican"},{"value":"O","valueLabel":"Other"}]</v>
       </c>
       <c r="O135" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P135" t="str">
         <v/>
@@ -9624,7 +9624,7 @@
         <v/>
       </c>
       <c r="O136" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P136" t="str">
         <v/>
@@ -9686,13 +9686,13 @@
         <v>No</v>
       </c>
       <c r="M137" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="N137" t="str">
         <v>[{"value":"AP","valueLabel":"Apostolic (Christian Protestant)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"RC","valueLabel":"Roman Catholic (Christian)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PE","valueLabel":"Pentecostal (Christian Protestant)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"A","valueLabel":"Anglican (Christian Protestant)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MD","valueLabel":"Methodist","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Ba","valueLabel":"Baptist (Christian Protestant)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"P","valueLabel":"Prespyterian (Christian Protestant)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SDA","valueLabel":"Seventh Day Adventist (SDA) (Christian Protestant)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CP","valueLabel":"Other Christian Protestant","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"J","valueLabel":"Jewish","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"JW","valueLabel":"Jehova's Witness","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MU","valueLabel":"Muslim","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AG","valueLabel":"Agnostic","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ATH","valueLabel":"Atheist","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Z","valueLabel":"Zion","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"O","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O137" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P137" t="str">
         <v/>
@@ -9828,7 +9828,7 @@
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"U","valueLabel":"Unknown"}]</v>
       </c>
       <c r="O139" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P139" t="str">
         <v/>
@@ -9955,7 +9955,7 @@
         <v>Yes</v>
       </c>
       <c r="L141" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="M141" t="str">
         <v/>
@@ -10097,7 +10097,7 @@
         <v/>
       </c>
       <c r="N143" t="str">
-        <v>[{"value":"R","valueLabel":"Positive"},{"value":"NR","valueLabel":"Negative"},{"value":"U","valueLabel":"Unknown"}]</v>
+        <v>[{"value":"R","valueLabel":"Positive"},{"value":"U","valueLabel":"Unknown"}]</v>
       </c>
       <c r="O143" t="str">
         <v>$MatHIVtest = 'Y'</v>
@@ -10165,7 +10165,7 @@
         <v>$HIVtestResult = 'R' or $HIVtestResult = 'NR'</v>
       </c>
       <c r="N144" t="str">
-        <v>[{"value":"Self","valueLabel":"Self-reported from mother"},{"value":"Doc","valueLabel":"From her documentation"},{"value":"","valueLabel":""}]</v>
+        <v>[{"value":"Self","valueLabel":"Self-reported from mother"},{"value":"Doc","valueLabel":"From her documentation"}]</v>
       </c>
       <c r="O144" t="str">
         <v>$MatHIVtest = 'Y'</v>
@@ -10209,10 +10209,10 @@
         <v>form</v>
       </c>
       <c r="F145" t="str">
-        <v>HAART</v>
+        <v>MaHAART</v>
       </c>
       <c r="G145" t="str">
-        <v>Maternal HAART Status</v>
+        <v>Is the mother on HAART?</v>
       </c>
       <c r="H145" t="str">
         <v>dropdown</v>
@@ -10280,7 +10280,7 @@
         <v>LengthHAART</v>
       </c>
       <c r="G146" t="str">
-        <v>Mother on HAART since when?</v>
+        <v>Maternal HAART Initiation</v>
       </c>
       <c r="H146" t="str">
         <v>dropdown</v>
@@ -10298,7 +10298,7 @@
         <v>No</v>
       </c>
       <c r="M146" t="str">
-        <v>$HAART = 'Y'</v>
+        <v>$MaHAART = 'Y'</v>
       </c>
       <c r="N146" t="str">
         <v>[{"value":"1stTrim","valueLabel":"1st Trimester or earlier"},{"value":"2ndTrim","valueLabel":"2nd Trimester"},{"value":"3rdTrim","valueLabel":"3rd Trimester more than 1 month before delivery"},{"value":"Late","valueLabel":"Less than 1 month before delivery"},{"value":"U","valueLabel":"Unknown"}]</v>
@@ -10366,7 +10366,7 @@
         <v>No</v>
       </c>
       <c r="M147" t="str">
-        <v>$HAART= 'Y'</v>
+        <v>$MaHAART = 'Y'</v>
       </c>
       <c r="N147" t="str">
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"NA","valueLabel":"Not applicable"}]</v>
@@ -10416,7 +10416,7 @@
         <v>VLNumber</v>
       </c>
       <c r="G148" t="str">
-        <v>Viral Load</v>
+        <v>Viral Load (copies/ml)</v>
       </c>
       <c r="H148" t="str">
         <v>number</v>
@@ -10638,13 +10638,13 @@
         <v>No</v>
       </c>
       <c r="M151" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="N151" t="str">
         <v>[{"value":"Y","valueLabel":"Yes","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"N","valueLabel":"No","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"U","valueLabel":"Not sure","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O151" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P151" t="str">
         <v/>
@@ -11182,13 +11182,13 @@
         <v>No</v>
       </c>
       <c r="M159" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="N159" t="str">
         <v>[{"value":"An","valueLabel":"Anaemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DM","valueLabel":"Diabetes","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HD","valueLabel":"Heart disease","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HTN","valueLabel":"Hypertension or pre-eclampsia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MAL","valueLabel":"Malaria","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"STD","valueLabel":"Sexually Transmitted Disease (other than HIV/syphilis)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"THY","valueLabel":"Thyroid disease / goitre","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TU","valueLabel":"Tuberculosis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OTH","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"U","valueLabel":"Unknown","disabledOtherOptionsIfSelected":true,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
       </c>
       <c r="O159" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P159" t="str">
         <v/>
@@ -11392,7 +11392,7 @@
         <v/>
       </c>
       <c r="O162" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P162" t="str">
         <v/>
@@ -11460,7 +11460,7 @@
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"U","valueLabel":"Unknown"}]</v>
       </c>
       <c r="O163" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P163" t="str">
         <v/>
@@ -11528,7 +11528,7 @@
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"U","valueLabel":"Unknown"}]</v>
       </c>
       <c r="O164" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P164" t="str">
         <v/>
@@ -11596,7 +11596,7 @@
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"U","valueLabel":"Unknown"}]</v>
       </c>
       <c r="O165" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P165" t="str">
         <v/>
@@ -11658,13 +11658,13 @@
         <v>No</v>
       </c>
       <c r="M166" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N166" t="str">
         <v>[{"value":"IPT0","valueLabel":"No SP doses","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"IPT1","valueLabel":"1 SP dose","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"IPT2","valueLabel":"2 SP doses","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"IPT3","valueLabel":"3 SP doses","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"IPT4","valueLabel":"4 SP doses","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"IPT5+","valueLabel":"5 or more SP doses","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"IPTU","valueLabel":"Not sure","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O166" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P166" t="str">
         <v/>
@@ -11726,13 +11726,13 @@
         <v>No</v>
       </c>
       <c r="M167" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="N167" t="str">
         <v>[{"value":"Y","valueLabel":"Yes","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"N","valueLabel":"No","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"U","valueLabel":"Not Sure","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O167" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P167" t="str">
         <v/>
@@ -11794,13 +11794,13 @@
         <v>No</v>
       </c>
       <c r="M168" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="N168" t="str">
         <v>[{"value":"SVB","valueLabel":"Significant Vaginal Bleeding","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Pre","valueLabel":"Pre-eclampsia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Conv","valueLabel":"Convulsions / Eclampsia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Poly","valueLabel":"Polyhydramnios","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Olig","valueLabel":"Oligohydramnios","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
       </c>
       <c r="O168" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P168" t="str">
         <v/>
@@ -12276,7 +12276,7 @@
         <v>[{"value":"NOPROM","valueLabel":"less than 18 hours"},{"value":"PROM","valueLabel":"greater than 18 hours"}]</v>
       </c>
       <c r="O175" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P175" t="str">
         <v/>
@@ -12338,13 +12338,13 @@
         <v>No</v>
       </c>
       <c r="M176" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="N176" t="str">
-        <v>[{"value":"PROM","valueLabel":"PROM more than 18 hrs","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MF","valueLabel":"Maternal fever in labour","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OL","valueLabel":"Offensive Liquor","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Pr2nd","valueLabel":"Prolonged second stage","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BBA","valueLabel":"Born Before Arrival (BBA)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Prem","valueLabel":"Prematurity &lt; 37 weeks","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
+        <v>[{"value":"PROM","valueLabel":"PROM more than 18 hrs","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MF","valueLabel":"Maternal fever in labour","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OL","valueLabel":"Offensive Liquor","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Pr2nd","valueLabel":"Prolonged second stage labour","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BBA","valueLabel":"Born Before Arrival (BBA)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Prem","valueLabel":"Prematurity &lt; 37 weeks","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
       </c>
       <c r="O176" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P176" t="str">
         <v/>
@@ -12412,7 +12412,7 @@
         <v>[{"value":"Vertex","valueLabel":"Vertex"},{"value":"Brow","valueLabel":"Brow"},{"value":"Breech","valueLabel":"Breech"},{"value":"Face","valueLabel":"Face"},{"value":"Unk","valueLabel":"Unknown"}]</v>
       </c>
       <c r="O177" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P177" t="str">
         <v/>
@@ -12480,7 +12480,7 @@
         <v>[{"value":"1","valueLabel":"Spontaneous Vaginal Delivery"},{"value":"7","valueLabel":"Induced Vaginal Delivery"},{"value":"6","valueLabel":"Breech extraction (vaginal)"},{"value":"2","valueLabel":"Vacuum extraction"},{"value":"3","valueLabel":"Forceps extraction"},{"value":"4","valueLabel":"Elective Ceasarian Section (ELCS)"},{"value":"5","valueLabel":"Emergency Ceasarian Section (EMCS)"}]</v>
       </c>
       <c r="O178" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P178" t="str">
         <v/>
@@ -12678,13 +12678,13 @@
         <v>No</v>
       </c>
       <c r="M181" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="N181" t="str">
         <v>[{"value":"Stim","valueLabel":"Stimulation","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Suc","valueLabel":"Suctioning","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"O2","valueLabel":"Oxygen","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BVM","valueLabel":"Bag Valve Mask Ventilation (BVM)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CPR","valueLabel":"Cardio Pulmonary Resuscitation (CPR)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Unk","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
       </c>
       <c r="O181" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P181" t="str">
         <v/>
@@ -12882,13 +12882,13 @@
         <v>No</v>
       </c>
       <c r="M184" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="N184" t="str">
         <v>[{"value":"DCC","valueLabel":"Delayed Cord Clamping (greater than 60 secs)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"S2S","valueLabel":"Skin to Skin (within 1st hour of life)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BF","valueLabel":"Breast Feeding (within 1st hour of life)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"U","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O184" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P184" t="str">
         <v/>
@@ -12956,7 +12956,7 @@
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"NS","valueLabel":"Not Sure"}]</v>
       </c>
       <c r="O185" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P185" t="str">
         <v/>
@@ -13024,7 +13024,7 @@
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"NS","valueLabel":"Not Sure"}]</v>
       </c>
       <c r="O186" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P186" t="str">
         <v/>
@@ -13837,7 +13837,7 @@
         <v/>
       </c>
       <c r="N198" t="str">
-        <v>[{"value":"An","valueLabel":"Anaemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BBA","valueLabel":"Born Before Arrival","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BI","valueLabel":"Birth Trauma","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Cong","valueLabel":"Congenital Abnormality","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CHD","valueLabel":"Consider Congenital Heart Disease","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Conv","valueLabel":"Convulsions","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Dhyd","valueLabel":"Dehydration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DF","valueLabel":"Difficulty Feeding","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DUM","valueLabel":"Abandoned baby","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HIVExp","valueLabel":"HIV Exposed","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HIVU","valueLabel":"HIV Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Syph_Exp","valueLabel":"Syphilis exposed","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HypogAs","valueLabel":"Hypoglycaemia (NOT symptomatic)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HypogSy","valueLabel":"Hypoglycaemia (symptomatic)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"RiHypog","valueLabel":"Risk of hypoglycaemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BA","valueLabel":"Hypoxic Ischaemic Encephalopathy","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"GSchis","valueLabel":"Gastroschisis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MJ","valueLabel":"Physiological Jaundice","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"LBW","valueLabel":"Low Birth Weight (1500-2499g)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"VLBW","valueLabel":"Very Low Birth Weight (1000-1499g)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ExLBW","valueLabel":"Extremely low birth weight (&lt;1000g)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MA","valueLabel":"Possible Meconium Aspiration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MecEx","valueLabel":"Meconium exposure (asymptomatic baby)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MiHypo","valueLabel":"Mild Hypothermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ModHypo","valueLabel":"Moderate Hypothermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SHypo","valueLabel":"Severe Hypothermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Hyperth","valueLabel":"Hyperthermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SEPS","valueLabel":"Suspected Neonatal Sepsis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Risk","valueLabel":"Risk factors for sepsis (asymptomatic baby)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ConMen","valueLabel":"Consider Meningitis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NB","valueLabel":"Normal Baby","disabledOtherOptionsIfSelected":true,"forbidWIth":[]},{"value":"PN","valueLabel":"Pneumonia /  Bronchiolitis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Prem","valueLabel":"Premature (32 to 37 weeks)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"VPrem","valueLabel":"Very Premature (28-31+6 weeks)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ExPrem","valueLabel":"Extremely Premature (&lt;28 weeks)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PremRD","valueLabel":"Premature baby with Respiratory Distress","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Safe","valueLabel":"Safekeeping","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TTN","valueLabel":"Transient Tachypnoea of Newborn (TTN)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OTH","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HBW","valueLabel":"Macrosomia (&gt;4000g)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TermRD","valueLabel":"Term with Respiratory Distress","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DJ","valueLabel":"Pathological Jaundice","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"sHIE","valueLabel":"Suspected Hypoxic Ischaemic Encephalopathy (HIE)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ApofPrem","valueLabel":"Apnoea of prematurity","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ProJ","valueLabel":"Prolonged Jaundice","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CleftLip","valueLabel":"Cleft lip","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CleftRD","valueLabel":"Cleft lip and/or palate with RD","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CleftPal","valueLabel":"Cleft palate","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Omph","valueLabel":"Omphalocele","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Myelo","valueLabel":"Myelomeningocele","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CDH","valueLabel":"Congenital dislocation of the hip (CDH)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MiTalipes","valueLabel":"Mild Talipes (club foot)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MoTalipes","valueLabel":"Moderate Talipes (club foot)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ConTet","valueLabel":"Consider Tetanus","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NecEnt","valueLabel":"Consider Necrotising Enterocolitis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"An","valueLabel":"Anaemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BBA","valueLabel":"Born before arrival","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BT","valueLabel":"Birth injury / Trauma","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Cong","valueLabel":"Congenital Abnormality","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CHD","valueLabel":"Consider Congenital Heart Disease","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Conv","valueLabel":"Convulsions","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Dhyd","valueLabel":"Dehydration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DF","valueLabel":"Difficulty Feeding","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DUM","valueLabel":"Abandoned baby","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HIVExp","valueLabel":"HIV Exposed","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HIVU","valueLabel":"HIV Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Syph_Exp","valueLabel":"Syphilis exposed","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HypogAs","valueLabel":"Hypoglycaemia (NOT symptomatic)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HypogSy","valueLabel":"Hypoglycaemia (symptomatic)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"RiHypog","valueLabel":"Risk of hypoglycaemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BA","valueLabel":"Hypoxic Ischaemic Encephalopathy","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"GSchis","valueLabel":"Gastroschisis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MJ","valueLabel":"Physiological Jaundice","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"LBW","valueLabel":"Low Birth Weight (1500-2499g)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"VLBW","valueLabel":"Very Low Birth Weight (1000-1499g)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ExLBW","valueLabel":"Extremely low birth weight (&lt;1000g)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MA","valueLabel":"Possible Meconium Aspiration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MecEx","valueLabel":"Meconium exposure (asymptomatic baby)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MiHypo","valueLabel":"Mild Hypothermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ModHypo","valueLabel":"Moderate Hypothermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SHypo","valueLabel":"Severe Hypothermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Hyperth","valueLabel":"Hyperthermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SEPS","valueLabel":"Suspected Neonatal Sepsis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Risk","valueLabel":"Risk factors for sepsis (asymptomatic baby)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ConMen","valueLabel":"Consider Meningitis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NB","valueLabel":"Normal Baby","disabledOtherOptionsIfSelected":true,"forbidWIth":[]},{"value":"PN","valueLabel":"Pneumonia /  Bronchiolitis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Prem","valueLabel":"Premature (32 to 37 weeks)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"VPrem","valueLabel":"Very Premature (28-31+6 weeks)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ExPrem","valueLabel":"Extremely Premature (&lt;28 weeks)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PremRD","valueLabel":"Premature baby with Respiratory Distress","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Safe","valueLabel":"Safekeeping","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TTN","valueLabel":"Transient Tachypnoea of Newborn (TTN)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OTH","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HBW","valueLabel":"Macrosomia (&gt;4000g)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TermRD","valueLabel":"Term with Respiratory Distress","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DJ","valueLabel":"Pathological Jaundice","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"sHIE","valueLabel":"Suspected Hypoxic Ischaemic Encephalopathy (HIE)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ApofPrem","valueLabel":"Apnoea of prematurity","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ProJ","valueLabel":"Prolonged Jaundice","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CleftLip","valueLabel":"Cleft lip","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CleftRD","valueLabel":"Cleft lip and/or palate with RD","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CleftPal","valueLabel":"Cleft palate","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Omph","valueLabel":"Omphalocele","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Myelo","valueLabel":"Myelomeningocele","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CDH","valueLabel":"Congenital dislocation of the hip (CDH)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MiTalipes","valueLabel":"Mild Talipes (club foot)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MoTalipes","valueLabel":"Moderate Talipes (club foot)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ConTet","valueLabel":"Consider Tetanus","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NecEnt","valueLabel":"Consider Necrotising Enterocolitis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O198" t="str">
         <v/>
@@ -13908,7 +13908,7 @@
         <v/>
       </c>
       <c r="O199" t="str">
-        <v>($DangerSigns = 'Grun' or $RR &gt; 60 or $SatsO2 &lt; 90 or $WOB = 'Mod' or $WOB = 'Sev' or $Diagnoses = 'RDN' or $AdmReason = 'PREMRDS') and $NobCPAP = false</v>
+        <v xml:space="preserve">($DangerSigns = 'Grun' or $RR &gt; 60 or $SatsO2 &lt; 90 or $WOB = 'Mod' or $WOB = 'Sev' or $AdmReason = 'PREMRDS') </v>
       </c>
       <c r="P199" t="str">
         <v/>
@@ -15208,7 +15208,7 @@
         <v>Chinhoyi Provincial Hospital</v>
       </c>
       <c r="C3" t="str">
-        <v>Born Before Arrival</v>
+        <v>Born before arrival</v>
       </c>
       <c r="D3" t="str">
         <v>Born before arrival</v>
@@ -15220,7 +15220,7 @@
         <v>e3cb5ede-7fc1-43aa-8d79-bd36a4cd332e</v>
       </c>
       <c r="G3" t="str">
-        <v>Born Before Arrival</v>
+        <v>Born before arrival</v>
       </c>
       <c r="H3" t="str">
         <v>7046</v>
@@ -15265,7 +15265,7 @@
         <v>BBA</v>
       </c>
       <c r="V3" t="str">
-        <v>Born Before Arrival</v>
+        <v>Born before arrival</v>
       </c>
       <c r="W3" t="str">
         <v/>
@@ -15285,19 +15285,19 @@
         <v>Chinhoyi Provincial Hospital</v>
       </c>
       <c r="C4" t="str">
-        <v>Birth Trauma</v>
+        <v>Birth injury / Trauma</v>
       </c>
       <c r="D4" t="str">
         <v>Birth Trauma</v>
       </c>
       <c r="E4" t="str">
-        <v>BI</v>
+        <v>BT</v>
       </c>
       <c r="F4" t="str">
         <v>ec2adc2a-3fa6-438d-89de-7e3b87f568c6</v>
       </c>
       <c r="G4" t="str">
-        <v>Birth Trauma</v>
+        <v>Birth injury / Trauma</v>
       </c>
       <c r="H4" t="str">
         <v>7047</v>
@@ -15339,10 +15339,10 @@
         <v>diagnosis</v>
       </c>
       <c r="U4" t="str">
-        <v>BI</v>
+        <v>BT</v>
       </c>
       <c r="V4" t="str">
-        <v>Birth Trauma</v>
+        <v>Birth injury / Trauma</v>
       </c>
       <c r="W4" t="str">
         <v/>
@@ -17732,7 +17732,7 @@
         <v>Chinhoyi Provincial Hospital</v>
       </c>
       <c r="C32" t="str">
-        <v>? Congenital Pneumonia</v>
+        <v>Congenital Pneumonia</v>
       </c>
       <c r="D32" t="str">
         <v>RDN - Congenital Pneumonia</v>
@@ -17744,7 +17744,7 @@
         <v>2f74e32f-d1a8-4a5a-b672-cee9b6d6fd38</v>
       </c>
       <c r="G32" t="str">
-        <v>? Congenital Pneumonia</v>
+        <v>Congenital Pneumonia</v>
       </c>
       <c r="H32" t="str">
         <v>7075</v>
@@ -17806,7 +17806,7 @@
         <v>CongPneu</v>
       </c>
       <c r="V32" t="str">
-        <v>? Congenital Pneumonia</v>
+        <v>Congenital Pneumonia</v>
       </c>
       <c r="W32" t="str">
         <v/>
